--- a/artfynd/A 2545-2020 artfynd.xlsx
+++ b/artfynd/A 2545-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121656304</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Berg, Anders Esplund, Pia Edfors, Enviro Planning</t>
+          <t>Enviro Planning, Pia Edfors, Anders Esplund, Sofia Berg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +785,7 @@
         <v>121656303</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sofia Berg, Anders Esplund, Pia Edfors, Enviro Planning</t>
+          <t>Enviro Planning, Pia Edfors, Anders Esplund, Sofia Berg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 2545-2020 artfynd.xlsx
+++ b/artfynd/A 2545-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121656304</v>
+        <v>121656303</v>
       </c>
       <c r="B2" t="n">
         <v>57373</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>333417</v>
+        <v>333359</v>
       </c>
       <c r="R2" t="n">
-        <v>6528333</v>
+        <v>6528350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121656303</v>
+        <v>121656304</v>
       </c>
       <c r="B3" t="n">
         <v>57373</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333359</v>
+        <v>333417</v>
       </c>
       <c r="R3" t="n">
-        <v>6528350</v>
+        <v>6528333</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 2545-2020 artfynd.xlsx
+++ b/artfynd/A 2545-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121656303</v>
+        <v>121656304</v>
       </c>
       <c r="B2" t="n">
         <v>57373</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>333359</v>
+        <v>333417</v>
       </c>
       <c r="R2" t="n">
-        <v>6528350</v>
+        <v>6528333</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121656304</v>
+        <v>121656303</v>
       </c>
       <c r="B3" t="n">
         <v>57373</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333417</v>
+        <v>333359</v>
       </c>
       <c r="R3" t="n">
-        <v>6528333</v>
+        <v>6528350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 2545-2020 artfynd.xlsx
+++ b/artfynd/A 2545-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121656304</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>121656303</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2545-2020 artfynd.xlsx
+++ b/artfynd/A 2545-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121656304</v>
+        <v>121656303</v>
       </c>
       <c r="B2" t="n">
         <v>57381</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>333417</v>
+        <v>333359</v>
       </c>
       <c r="R2" t="n">
-        <v>6528333</v>
+        <v>6528350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121656303</v>
+        <v>121656304</v>
       </c>
       <c r="B3" t="n">
         <v>57381</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333359</v>
+        <v>333417</v>
       </c>
       <c r="R3" t="n">
-        <v>6528350</v>
+        <v>6528333</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
